--- a/db_tables/HighScores.xlsx
+++ b/db_tables/HighScores.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>seq</t>
   </si>
@@ -21,6 +21,15 @@
   </si>
   <si>
     <t>level</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Nadav</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
 </sst>
 </file>
@@ -65,7 +74,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -79,6 +88,17 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
